--- a/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-02-15--2024-03-22/report.xlsx
+++ b/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-02-15--2024-03-22/report.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Updated: Feb 04, 2025</t>
+          <t>Updated: Mar 04, 2025</t>
         </is>
       </c>
     </row>
